--- a/Unused/b-Office/BOM表.xlsx
+++ b/Unused/b-Office/BOM表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OneHistory\HistoryClio\0000-000-Template\Unused\b-Office\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMINI~1\AppData\Local\Temp\claude\C--Users-Administrator--claude\0cab2c21-87c3-47d0-bf84-58a46c9e0e75\scratchpad\office\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53091D4D-9DBD-41C1-8855-4A821411AE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ED7E7B7-E338-434B-BCFE-771050B0FFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1875" yWindow="4170" windowWidth="28800" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Revision History" sheetId="1" r:id="rId1"/>
@@ -194,7 +194,7 @@
     <font>
       <b/>
       <sz val="9.5"/>
-      <color rgb="FFFBFAF7"/>
+      <color rgb="FF26231E"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
@@ -234,7 +234,7 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FFFBFAF7"/>
+      <color rgb="FF26231E"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
@@ -279,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -290,17 +290,25 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
+      <top style="thick">
+        <color rgb="FF26231E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF26231E"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF6A6458"/>
+        <color rgb="FFD5D1C8"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
+      <top style="thick">
+        <color rgb="FF26231E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF26231E"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -384,14 +392,56 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF26231E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF6A6458"/>
+        <color rgb="FFD5D1C8"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FF26231E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF26231E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD5D1C8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF26231E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD5D1C8"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FF6A6458"/>
+        <color rgb="FFD5D1C8"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FF26231E"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -420,15 +470,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -455,7 +505,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -467,35 +517,41 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1082,139 +1138,139 @@
     </row>
     <row r="4" spans="1:16" ht="8.1" customHeight="1"/>
     <row r="5" spans="1:16" ht="18" customHeight="1">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="26" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="27"/>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="27"/>
-      <c r="I5" s="26" t="s">
+      <c r="H5" s="21"/>
+      <c r="I5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="27"/>
-      <c r="K5" s="26" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="27"/>
-      <c r="M5" s="26" t="s">
+      <c r="L5" s="21"/>
+      <c r="M5" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="27"/>
-      <c r="O5" s="26" t="s">
+      <c r="N5" s="21"/>
+      <c r="O5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="P5" s="27"/>
+      <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="20" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="20" t="s">
+      <c r="F6" s="23"/>
+      <c r="G6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="20" t="s">
+      <c r="H6" s="23"/>
+      <c r="I6" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="21"/>
-      <c r="K6" s="25" t="s">
+      <c r="J6" s="23"/>
+      <c r="K6" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="21"/>
-      <c r="M6" s="25" t="s">
+      <c r="L6" s="23"/>
+      <c r="M6" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="21"/>
-      <c r="O6" s="25" t="s">
+      <c r="N6" s="23"/>
+      <c r="O6" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="21"/>
+      <c r="P6" s="23"/>
     </row>
     <row r="7" spans="1:16" ht="12" customHeight="1"/>
     <row r="8" spans="1:16" ht="21.95" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22" t="s">
+      <c r="G8" s="24"/>
+      <c r="H8" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="22" t="s">
+      <c r="J8" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="22" t="s">
+      <c r="L8" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="M8" s="22" t="s">
+      <c r="M8" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="N8" s="22" t="s">
+      <c r="N8" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="O8" s="22" t="s">
+      <c r="O8" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="P8" s="22" t="s">
+      <c r="P8" s="24" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="21.95" customHeight="1">
-      <c r="A9" s="23"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
     </row>
     <row r="10" spans="1:16" ht="21" customHeight="1">
       <c r="A10" s="13">
@@ -1706,21 +1762,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="K6:L6"/>
     <mergeCell ref="C1:P1"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="F8:G8"/>
@@ -1737,6 +1778,21 @@
     <mergeCell ref="O8:O9"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="H8:H9"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="J8:J9"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="1">

--- a/Unused/b-Office/BOM表.xlsx
+++ b/Unused/b-Office/BOM表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMINI~1\AppData\Local\Temp\claude\C--Users-Administrator--claude\0cab2c21-87c3-47d0-bf84-58a46c9e0e75\scratchpad\office\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ED7E7B7-E338-434B-BCFE-771050B0FFF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0042E3B-5259-4C3B-89D6-CB37C8E406D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1875" yWindow="4170" windowWidth="28800" windowHeight="15435" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,17 +266,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26231E"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="18">
@@ -522,7 +517,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -552,6 +546,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -604,6 +599,88 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>361950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="矩形: 圆角 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DB24D44-A7BF-D982-19F5-89A7E642A6B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1676400" y="38100"/>
+          <a:ext cx="7772400" cy="323850"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 21569"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="26231E"/>
+        </a:solidFill>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="25400" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -642,6 +719,88 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>361950</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="矩形: 圆角 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{437A15DF-38CA-C23A-DCED-AEAE03534AC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1524000" y="38100"/>
+          <a:ext cx="14630400" cy="323850"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 21569"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="26231E"/>
+        </a:solidFill>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:effectLst/>
+        <a:extLst>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="25400" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -943,10 +1102,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.1" customHeight="1">
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
     </row>
     <row r="2" spans="1:5" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:5" ht="30" customHeight="1">
@@ -1115,20 +1274,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="32.1" customHeight="1">
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
     </row>
     <row r="2" spans="1:16" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:16" ht="30" customHeight="1">
@@ -1138,139 +1297,139 @@
     </row>
     <row r="4" spans="1:16" ht="8.1" customHeight="1"/>
     <row r="5" spans="1:16" ht="18" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="27" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="21"/>
-      <c r="G5" s="27" t="s">
+      <c r="F5" s="20"/>
+      <c r="G5" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="27" t="s">
+      <c r="H5" s="20"/>
+      <c r="I5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="27" t="s">
+      <c r="J5" s="20"/>
+      <c r="K5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="21"/>
-      <c r="M5" s="27" t="s">
+      <c r="L5" s="20"/>
+      <c r="M5" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="21"/>
-      <c r="O5" s="27" t="s">
+      <c r="N5" s="20"/>
+      <c r="O5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="P5" s="21"/>
+      <c r="P5" s="20"/>
     </row>
     <row r="6" spans="1:16" ht="27.95" customHeight="1">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="22" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="22" t="s">
+      <c r="F6" s="22"/>
+      <c r="G6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="23"/>
-      <c r="I6" s="22" t="s">
+      <c r="H6" s="22"/>
+      <c r="I6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="26" t="s">
+      <c r="J6" s="22"/>
+      <c r="K6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="23"/>
-      <c r="M6" s="26" t="s">
+      <c r="L6" s="22"/>
+      <c r="M6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="23"/>
-      <c r="O6" s="26" t="s">
+      <c r="N6" s="22"/>
+      <c r="O6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="23"/>
+      <c r="P6" s="22"/>
     </row>
     <row r="7" spans="1:16" ht="12" customHeight="1"/>
     <row r="8" spans="1:16" ht="21.95" customHeight="1">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24" t="s">
+      <c r="G8" s="23"/>
+      <c r="H8" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="24" t="s">
+      <c r="L8" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="N8" s="24" t="s">
+      <c r="N8" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="O8" s="24" t="s">
+      <c r="O8" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="P8" s="24" t="s">
+      <c r="P8" s="23" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="21.95" customHeight="1">
-      <c r="A9" s="31"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
       <c r="F9" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
     </row>
     <row r="10" spans="1:16" ht="21" customHeight="1">
       <c r="A10" s="13">
@@ -1745,11 +1904,11 @@
       <c r="J30" s="16"/>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
-      <c r="M30" s="28" t="s">
+      <c r="M30" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
       <c r="P30" s="17">
         <f>SUM(P10:P29)</f>
         <v>0</v>
